--- a/artfynd/A 30886-2025 artfynd.xlsx
+++ b/artfynd/A 30886-2025 artfynd.xlsx
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126546297</v>
+        <v>126538896</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565015</v>
+        <v>565074</v>
       </c>
       <c r="R2" t="n">
-        <v>6993265</v>
+        <v>6993143</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -748,12 +751,18 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lunglav på intilliggande granar</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,48 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126538896</v>
+        <v>126546297</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565074</v>
+        <v>565015</v>
       </c>
       <c r="R3" t="n">
-        <v>6993143</v>
+        <v>6993265</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -848,18 +854,12 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lunglav på intilliggande granar</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30886-2025 artfynd.xlsx
+++ b/artfynd/A 30886-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126538896</v>
       </c>
       <c r="B2" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126546297</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126538809</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>126538768</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>126539006</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>126538974</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126538997</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>126538832</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>126554435</v>
       </c>
       <c r="B11" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>126554328</v>
       </c>
       <c r="B12" t="n">
-        <v>105381</v>
+        <v>105456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30886-2025 artfynd.xlsx
+++ b/artfynd/A 30886-2025 artfynd.xlsx
@@ -1584,7 +1584,7 @@
         <v>126554435</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>126554328</v>
       </c>
       <c r="B12" t="n">
-        <v>105456</v>
+        <v>105462</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30886-2025 artfynd.xlsx
+++ b/artfynd/A 30886-2025 artfynd.xlsx
@@ -1584,7 +1584,7 @@
         <v>126554435</v>
       </c>
       <c r="B11" t="n">
-        <v>98476</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>126554328</v>
       </c>
       <c r="B12" t="n">
-        <v>105462</v>
+        <v>105456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30886-2025 artfynd.xlsx
+++ b/artfynd/A 30886-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>126538896</v>
       </c>
       <c r="B2" t="n">
-        <v>80114</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,45 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126546297</v>
+        <v>126538912</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565015</v>
+        <v>565028</v>
       </c>
       <c r="R3" t="n">
-        <v>6993265</v>
+        <v>6993297</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -854,12 +857,18 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Även på intilliggande granar</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,49 +887,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126538809</v>
+        <v>126538974</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564987</v>
+        <v>565002</v>
       </c>
       <c r="R4" t="n">
-        <v>6993296</v>
+        <v>6993234</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -961,7 +966,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -980,49 +984,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126538768</v>
+        <v>126538997</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565087</v>
+        <v>565015</v>
       </c>
       <c r="R5" t="n">
-        <v>6993174</v>
+        <v>6993265</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1063,7 +1063,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1082,10 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126539033</v>
+        <v>126539006</v>
       </c>
       <c r="B6" t="n">
-        <v>56840</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,46 +1092,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564970</v>
+        <v>565039</v>
       </c>
       <c r="R6" t="n">
-        <v>6993323</v>
+        <v>6993258</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126539006</v>
+        <v>126539215</v>
       </c>
       <c r="B7" t="n">
-        <v>80114</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1223,10 +1213,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565039</v>
+        <v>565096</v>
       </c>
       <c r="R7" t="n">
-        <v>6993258</v>
+        <v>6993194</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1259,6 +1249,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Även på intilliggande granar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,48 +1280,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126538974</v>
+        <v>126539033</v>
       </c>
       <c r="B8" t="n">
-        <v>80114</v>
+        <v>57132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565002</v>
+        <v>564970</v>
       </c>
       <c r="R8" t="n">
-        <v>6993234</v>
+        <v>6993323</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,32 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126538997</v>
+        <v>126554435</v>
       </c>
       <c r="B9" t="n">
-        <v>80114</v>
+        <v>99153</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565015</v>
+        <v>564987</v>
       </c>
       <c r="R9" t="n">
-        <v>6993265</v>
+        <v>6993296</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1479,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126538832</v>
+        <v>126538768</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565002</v>
+        <v>565087</v>
       </c>
       <c r="R10" t="n">
-        <v>6993234</v>
+        <v>6993174</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1581,35 +1585,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126554435</v>
+        <v>126538809</v>
       </c>
       <c r="B11" t="n">
-        <v>98476</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
@@ -1660,6 +1668,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1678,45 +1687,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126554328</v>
+        <v>126538832</v>
       </c>
       <c r="B12" t="n">
-        <v>105462</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storsvedjeberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565015</v>
+        <v>565002</v>
       </c>
       <c r="R12" t="n">
-        <v>6993265</v>
+        <v>6993234</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1757,6 +1770,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1772,6 +1786,394 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126538848</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>564962</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6993110</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126546297</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>565015</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6993265</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126554328</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>565015</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6993265</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126538920</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storsvedjeberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>565028</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6993297</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30886-2025 artfynd.xlsx
+++ b/artfynd/A 30886-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126538896</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126538912</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126538974</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126538997</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126539006</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1277,6 +1307,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126539215</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126539033</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126554435</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126538768</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1684,6 +1734,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126538809</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1786,6 +1841,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126538832</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1883,6 +1943,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126538848</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1980,6 +2045,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126546297</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2077,6 +2147,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126554328</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2174,8 +2249,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126538920</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>